--- a/tabela1-1_mod_habilidades_e_magias.xlsx
+++ b/tabela1-1_mod_habilidades_e_magias.xlsx
@@ -746,10 +746,8 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="14.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="10.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="14.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="0" width="14.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
